--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10614,10 +10614,10 @@
         <v>0.002310791971430208</v>
       </c>
       <c r="J56" t="n">
-        <v>11032</v>
+        <v>11036</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>51794</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.04351726144297905</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -38071,7 +38071,7 @@
         <v>0.0572493920090118</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,19 +10599,19 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>51794</v>
+        <v>50256</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>690</v>
+        <v>2096</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.002310791971430208</v>
+        <v>-0.0002100719974027462</v>
       </c>
       <c r="J56" t="n">
         <v>11036</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7423405228260042</v>
+        <v>-0.7416908618581907</v>
       </c>
       <c r="J57" t="n">
         <v>9197</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.04351726144297905</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -38071,7 +38071,7 @@
         <v>0.0572493920090118</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.04351726144297905</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -34538,10 +34538,10 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7321</v>
+        <v>7318</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -38071,7 +38071,7 @@
         <v>0.0572493920090118</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10614,7 +10614,7 @@
         <v>-0.0002100719974027462</v>
       </c>
       <c r="J56" t="n">
-        <v>11036</v>
+        <v>11037</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -21258,7 +21258,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6430</v>
+        <v>6437</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -34538,10 +34538,10 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7318</v>
+        <v>7321</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -38062,13 +38062,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>242145</v>
+        <v>242204</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.0572493920090118</v>
+        <v>0.0575069968083202</v>
       </c>
       <c r="E56" t="n">
         <v>4</v>
@@ -38086,7 +38086,7 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17513</v>
+        <v>17519</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -38105,7 +38105,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.05042846228499453</v>
+        <v>-0.05065977440504699</v>
       </c>
       <c r="E57" t="n">
         <v>7</v>
@@ -45182,7 +45182,7 @@
         <v>3.897708795269771</v>
       </c>
       <c r="J56" t="n">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -3518,7 +3518,7 @@
         <v>0.01042179763046691</v>
       </c>
       <c r="J56" t="n">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.04351726144297905</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -34538,7 +34538,7 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7321</v>
+        <v>7320</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -38062,16 +38062,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>242204</v>
+        <v>242278</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.0575069968083202</v>
+        <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -38086,7 +38086,7 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17519</v>
+        <v>17526</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -38105,7 +38105,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.05065977440504699</v>
+        <v>-0.05094973542789688</v>
       </c>
       <c r="E57" t="n">
         <v>7</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -45182,7 +45182,7 @@
         <v>3.897708795269771</v>
       </c>
       <c r="J56" t="n">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -7066,7 +7066,7 @@
         <v>-0.3835986967480174</v>
       </c>
       <c r="J56" t="n">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -10599,7 +10599,7 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -10614,7 +10614,7 @@
         <v>-0.0002100719974027462</v>
       </c>
       <c r="J56" t="n">
-        <v>11037</v>
+        <v>11041</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34514,16 +34514,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>86086</v>
+        <v>87522</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.04351726144297905</v>
+        <v>0.06092416602017067</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -34557,7 +34557,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.05652487047835885</v>
+        <v>-0.07200475309065149</v>
       </c>
       <c r="E57" t="n">
         <v>7</v>
@@ -38071,7 +38071,7 @@
         <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -41634,7 +41634,7 @@
         <v>0.08732939498879609</v>
       </c>
       <c r="J56" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -45182,7 +45182,7 @@
         <v>3.897708795269771</v>
       </c>
       <c r="J56" t="n">
-        <v>3784</v>
+        <v>3788</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3521,7 +3521,7 @@
         <v>2246</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -21261,7 +21261,7 @@
         <v>6437</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -34541,7 +34541,7 @@
         <v>7320</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -38089,7 +38089,7 @@
         <v>17526</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -38089,7 +38089,7 @@
         <v>17526</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -41637,7 +41637,7 @@
         <v>1495</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3518,10 +3518,10 @@
         <v>0.01042179763046691</v>
       </c>
       <c r="J56" t="n">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -17710,7 +17710,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -21258,10 +21258,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -24806,7 +24806,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -34538,10 +34538,10 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7320</v>
+        <v>7322</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -38086,10 +38086,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17526</v>
+        <v>17531</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -41634,10 +41634,10 @@
         <v>0.08732939498879609</v>
       </c>
       <c r="J56" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.05074135509415496</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -10614,7 +10614,7 @@
         <v>-0.0002100719974027462</v>
       </c>
       <c r="J56" t="n">
-        <v>11041</v>
+        <v>11045</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.06092416602017067</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -34538,7 +34538,7 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7322</v>
+        <v>7323</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -38071,7 +38071,7 @@
         <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>33003</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10614,7 +10614,7 @@
         <v>-0.0002100719974027462</v>
       </c>
       <c r="J56" t="n">
-        <v>11045</v>
+        <v>11043</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -7066,7 +7066,7 @@
         <v>-0.3835986967480174</v>
       </c>
       <c r="J56" t="n">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>165331</v>
+        <v>165601</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.05074135509415496</v>
+        <v>0.0524573077338621</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -10608,16 +10608,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2096</v>
+        <v>2151</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.0002100719974027462</v>
+        <v>0.0008402879896109848</v>
       </c>
       <c r="J56" t="n">
-        <v>11043</v>
+        <v>11071</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2037065039224344</v>
+        <v>-0.205004800695648</v>
       </c>
       <c r="E57" t="n">
         <v>7</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7416908618581907</v>
+        <v>-0.7419619516476806</v>
       </c>
       <c r="J57" t="n">
         <v>9197</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21258,7 +21258,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6440</v>
+        <v>6442</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.06092416602017067</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -34538,7 +34538,7 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7323</v>
+        <v>7333</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -38071,7 +38071,7 @@
         <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -38086,10 +38086,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17531</v>
+        <v>17548</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,22 +45167,22 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
-        <v>33003</v>
+        <v>32739</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3.897708795269771</v>
+        <v>3.882631189948263</v>
       </c>
       <c r="J56" t="n">
-        <v>3788</v>
+        <v>3790</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -45216,7 +45216,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.8678055111218422</v>
+        <v>-0.8673972934516061</v>
       </c>
       <c r="J57" t="n">
         <v>3474</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.06092416602017067</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -38071,7 +38071,7 @@
         <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -38086,10 +38086,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17548</v>
+        <v>17551</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>32739</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>38509</v>
@@ -7051,7 +7051,7 @@
         <v>0.02103231050599472</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>30019</v>
@@ -10599,7 +10599,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>50256</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -34523,7 +34523,7 @@
         <v>0.06092416602017067</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>58530</v>
@@ -38071,7 +38071,7 @@
         <v>0.05783009435321548</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>37132</v>
@@ -38086,10 +38086,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J56" t="n">
-        <v>17551</v>
+        <v>17552</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -41619,7 +41619,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>49124</v>
@@ -45167,7 +45167,7 @@
         <v>0.07069484428160168</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>32739</v>
@@ -48715,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52263,7 +52263,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -7066,7 +7066,7 @@
         <v>-0.3835986967480174</v>
       </c>
       <c r="J56" t="n">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -10617,7 +10617,7 @@
         <v>11071</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -34538,7 +34538,7 @@
         <v>0.2554847394880209</v>
       </c>
       <c r="J56" t="n">
-        <v>7333</v>
+        <v>7331</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>-0.0002021619436087096</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>37132</v>
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04176083012381832</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10984,7 +10984,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11071</v>
+        <v>11073</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -21739,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6442</v>
+        <v>6446</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -38752,7 +38752,7 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17552</v>
+        <v>17555</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -45922,7 +45922,7 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J64" t="n">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -21742,7 +21742,7 @@
         <v>6446</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -38755,7 +38755,7 @@
         <v>17555</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3817,7 +3817,7 @@
         <v>2249</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -38755,7 +38755,7 @@
         <v>17555</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -45925,7 +45925,7 @@
         <v>3791</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -3814,10 +3814,10 @@
         <v>2.565813106173346e-05</v>
       </c>
       <c r="J64" t="n">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -10984,7 +10984,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11073</v>
+        <v>11081</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21715,16 +21715,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>84074</v>
+        <v>84114</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.0002021619436087096</v>
+        <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21739,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6446</v>
+        <v>6448</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -21758,7 +21758,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.04600708899302995</v>
+        <v>-0.04646075564115367</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25324,7 +25324,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -35167,7 +35167,7 @@
         <v>0.2347842277297364</v>
       </c>
       <c r="J64" t="n">
-        <v>7331</v>
+        <v>7338</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>37132</v>
@@ -38752,10 +38752,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17555</v>
+        <v>17559</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04176083012381832</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -45922,7 +45922,7 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J64" t="n">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -35170,7 +35170,7 @@
         <v>7338</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -35170,7 +35170,7 @@
         <v>7338</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10984,7 +10984,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11081</v>
+        <v>11089</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -21739,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -35167,10 +35167,10 @@
         <v>0.2347842277297364</v>
       </c>
       <c r="J64" t="n">
-        <v>7338</v>
+        <v>7340</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -38752,7 +38752,7 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17559</v>
+        <v>17561</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -10987,7 +10987,7 @@
         <v>11089</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>37132</v>
@@ -38752,10 +38752,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17561</v>
+        <v>17563</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04176083012381832</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.0524573077338621</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>37132</v>
@@ -38752,10 +38752,10 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17563</v>
+        <v>17567</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04176083012381832</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -21739,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -38752,7 +38752,7 @@
         <v>0.2054857204382116</v>
       </c>
       <c r="J64" t="n">
-        <v>17567</v>
+        <v>17568</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -45898,13 +45898,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>65458</v>
+        <v>65668</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.04176083012381832</v>
+        <v>0.04510296972976414</v>
       </c>
       <c r="E64" t="n">
         <v>11</v>
@@ -45941,7 +45941,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.2369763818020716</v>
+        <v>-0.239416458549065</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10960,16 +10960,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>165601</v>
+        <v>159612</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.0524573077338621</v>
+        <v>0.01439493603309882</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -10987,7 +10987,7 @@
         <v>11089</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1517200983085851</v>
+        <v>-0.1198907350324537</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -35170,7 +35170,7 @@
         <v>7340</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -38737,25 +38737,25 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>37132</v>
+        <v>38548</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>7653</v>
+        <v>7793</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.2054857204382116</v>
+        <v>0.2473688460606713</v>
       </c>
       <c r="J64" t="n">
         <v>17568</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -38786,7 +38786,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.4881098582114548</v>
+        <v>-0.5052976845557929</v>
       </c>
       <c r="J65" t="n">
         <v>12026</v>
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04510296972976414</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
